--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-geplanteabgabentx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-geplanteabgabentx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-geplanteabgabentx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-geplanteabgabentx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
